--- a/config/generated/templates/ConfigManifest.xlsx
+++ b/config/generated/templates/ConfigManifest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>@table</t>
   </si>
@@ -40,7 +40,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>857f0dc27c73bc6d</t>
+    <t>2b0b6fe6d3b06bdc</t>
   </si>
   <si>
     <t>#name</t>
@@ -52,30 +52,9 @@
     <t>snapshot_date</t>
   </si>
   <si>
-    <t>data_revision</t>
-  </si>
-  <si>
-    <t>required_rules_revision</t>
-  </si>
-  <si>
     <t>sora_cli_version</t>
   </si>
   <si>
-    <t>numeric_policy_revision</t>
-  </si>
-  <si>
-    <t>rng_algorithm_revision</t>
-  </si>
-  <si>
-    <t>state_hash_revision</t>
-  </si>
-  <si>
-    <t>replay_format_version</t>
-  </si>
-  <si>
-    <t>coverage_manifest_sha256</t>
-  </si>
-  <si>
     <t>#field</t>
   </si>
   <si>
@@ -95,12 +74,6 @@
   </si>
   <si>
     <t>length=10..10</t>
-  </si>
-  <si>
-    <t>length=1..80</t>
-  </si>
-  <si>
-    <t>length=64..64</t>
   </si>
   <si>
     <t>#desc</t>
@@ -520,22 +493,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" style="5" customWidth="1"/>
-    <col min="3" max="4" width="13.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1">
+    <row r="2" spans="1:10" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -578,31 +545,10 @@
       <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
@@ -613,66 +559,24 @@
       <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="C4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -683,77 +587,28 @@
       <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="42" customHeight="1">
+    <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/generated/templates/ConfigManifest.xlsx
+++ b/config/generated/templates/ConfigManifest.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>2b0b6fe6d3b06bdc</t>
+    <t>83afef1dfbfc1900</t>
   </si>
   <si>
     <t>#name</t>
@@ -64,7 +64,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
